--- a/Alexander Korns - Grade Calculator Project.xlsx
+++ b/Alexander Korns - Grade Calculator Project.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5521BA6-93CE-E244-B139-F8645B7D0C81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" activeTab="6" xr2:uid="{316FBA45-DAF0-7548-AAC6-82DED938C6AE}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" activeTab="3" xr2:uid="{316FBA45-DAF0-7548-AAC6-82DED938C6AE}"/>
   </bookViews>
   <sheets>
     <sheet name="documentation" sheetId="2" r:id="rId1"/>

--- a/Alexander Korns - Grade Calculator Project.xlsx
+++ b/Alexander Korns - Grade Calculator Project.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/997822/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5521BA6-93CE-E244-B139-F8645B7D0C81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59F4DF2D-3A11-ED48-A6B0-7AA077E9EB6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" activeTab="3" xr2:uid="{316FBA45-DAF0-7548-AAC6-82DED938C6AE}"/>
   </bookViews>
   <sheets>
     <sheet name="documentation" sheetId="2" r:id="rId1"/>
     <sheet name="overall" sheetId="1" r:id="rId2"/>
-    <sheet name="quarter_1" sheetId="3" r:id="rId3"/>
-    <sheet name="quarter_2" sheetId="4" r:id="rId4"/>
-    <sheet name="quarter_3" sheetId="8" r:id="rId5"/>
-    <sheet name="quarter_4" sheetId="9" r:id="rId6"/>
-    <sheet name="grading_legend" sheetId="7" r:id="rId7"/>
+    <sheet name="scenario" sheetId="10" r:id="rId3"/>
+    <sheet name="quarter_1" sheetId="3" r:id="rId4"/>
+    <sheet name="quarter_2" sheetId="4" r:id="rId5"/>
+    <sheet name="quarter_3" sheetId="8" r:id="rId6"/>
+    <sheet name="quarter_4" sheetId="9" r:id="rId7"/>
+    <sheet name="grading_legend" sheetId="7" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="111">
   <si>
     <t>Grade</t>
   </si>
@@ -372,13 +373,19 @@
   </si>
   <si>
     <t>End Grade</t>
+  </si>
+  <si>
+    <t>Scenario: Fail all the homeworks and labs but lock in on quizzes and exams for every quarter</t>
+  </si>
+  <si>
+    <t>There's no explicitly defined summative and formative assignments in the syllabus</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -413,6 +420,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="16"/>
       <color theme="1"/>
@@ -432,8 +446,34 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow (Body)"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -444,6 +484,18 @@
       <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4EA72E"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -539,7 +591,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -560,19 +612,93 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="27">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -811,7 +937,7 @@
           <xdr:col>7</xdr:col>
           <xdr:colOff>342900</xdr:colOff>
           <xdr:row>31</xdr:row>
-          <xdr:rowOff>152400</xdr:rowOff>
+          <xdr:rowOff>76200</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -853,6 +979,94 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>596900</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7BC2BC4E-BACF-B4AB-9E2C-CF092FF70595}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7200900" y="660400"/>
+          <a:ext cx="4699000" cy="1981200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>558800</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>200802</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8E409E8-42B1-B153-53D4-4DB1C6E88E7E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6337300" y="3086100"/>
+          <a:ext cx="7772400" cy="2194702"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1173,9 +1387,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{309531D4-4174-954A-9F3A-54A71D99C7A6}">
-  <dimension ref="A1"/>
+  <dimension ref="I30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <sheetData>
+    <row r="30" spans="9:9" ht="22" x14ac:dyDescent="0.3">
+      <c r="I30" s="41" t="s">
+        <v>110</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <drawing r:id="rId1"/>
@@ -1196,7 +1416,7 @@
                 <xdr:col>7</xdr:col>
                 <xdr:colOff>342900</xdr:colOff>
                 <xdr:row>31</xdr:row>
-                <xdr:rowOff>152400</xdr:rowOff>
+                <xdr:rowOff>76200</xdr:rowOff>
               </to>
             </anchor>
           </objectPr>
@@ -1218,6 +1438,11 @@
     <col min="2" max="2" width="17.33203125" customWidth="1"/>
     <col min="4" max="4" width="15.33203125" customWidth="1"/>
     <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="8" max="8" width="10.83203125" customWidth="1"/>
+    <col min="11" max="11" width="10.83203125" customWidth="1"/>
+    <col min="14" max="14" width="10.83203125" customWidth="1"/>
+    <col min="17" max="17" width="10.83203125" customWidth="1"/>
+    <col min="20" max="20" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -1241,7 +1466,7 @@
       </c>
       <c r="C3" s="24">
         <f>quarter_1!O7</f>
-        <v>92.585714285714289</v>
+        <v>91.614285714285714</v>
       </c>
       <c r="D3" s="19" t="str">
         <f>VLOOKUP(C3, grading_legend!$B$3:$E$7, 3, TRUE)</f>
@@ -1258,15 +1483,15 @@
       </c>
       <c r="C4" s="24">
         <f>quarter_2!O7</f>
-        <v>49.612499999999997</v>
+        <v>87.5</v>
       </c>
       <c r="D4" s="19" t="str">
         <f>VLOOKUP(C4, grading_legend!$B$3:$E$7, 3, TRUE)</f>
-        <v>E</v>
+        <v>B</v>
       </c>
       <c r="E4" s="12">
         <f>VLOOKUP(C4, grading_legend!$B$3:$E$7, 4, TRUE)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.2">
@@ -1275,15 +1500,15 @@
       </c>
       <c r="C5" s="19">
         <f>AVERAGE(quarter_1!L5,quarter_2!L5)</f>
-        <v>67.125</v>
+        <v>100</v>
       </c>
       <c r="D5" s="19" t="str">
         <f>VLOOKUP(C5, grading_legend!$B$3:$E$7, 3, TRUE)</f>
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="E5" s="12">
         <f>VLOOKUP(C5, grading_legend!$B$3:$E$7, 4, TRUE)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.2">
@@ -1292,7 +1517,7 @@
       </c>
       <c r="C6" s="24">
         <f>quarter_3!O7</f>
-        <v>92.585714285714289</v>
+        <v>90.685714285714283</v>
       </c>
       <c r="D6" s="19" t="str">
         <f>VLOOKUP(C6, grading_legend!$B$3:$E$7, 3, TRUE)</f>
@@ -1309,7 +1534,7 @@
       </c>
       <c r="C7" s="24">
         <f>quarter_4!O7</f>
-        <v>79.7</v>
+        <v>87.9</v>
       </c>
       <c r="D7" s="19" t="str">
         <f>VLOOKUP(C7, grading_legend!$B$3:$E$7, 3, TRUE)</f>
@@ -1343,11 +1568,11 @@
       </c>
       <c r="C9" s="24">
         <f>0.8*AVERAGE(C3,C4,C6,C7) + 0.2*AVERAGE(C5,C8)</f>
-        <v>79.609285714285718</v>
+        <v>91.539999999999992</v>
       </c>
       <c r="D9" s="19" t="str">
         <f>VLOOKUP(C9, grading_legend!$B$3:$E$7, 3, TRUE)</f>
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="E9" s="12"/>
     </row>
@@ -1357,11 +1582,11 @@
       </c>
       <c r="C10" s="19">
         <f>VLOOKUP(C9, grading_legend!$B$3:$G$7, 6, TRUE)</f>
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="D10" s="19" t="str">
         <f>VLOOKUP(C10, grading_legend!$G$3:$H$7, 2, TRUE)</f>
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="E10" s="12"/>
     </row>
@@ -1371,14 +1596,14 @@
       </c>
       <c r="C11" s="25" t="str">
         <f>D10</f>
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="D11" s="25"/>
       <c r="E11" s="14"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C3:C9">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="lessThan">
       <formula>75</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1387,6 +1612,449 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{046EEEFD-F47D-594A-9D11-82F7D920307F}">
+  <dimension ref="B1:T14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="17.83203125" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="17.5" customWidth="1"/>
+    <col min="7" max="7" width="22.1640625" customWidth="1"/>
+    <col min="10" max="10" width="17.1640625" customWidth="1"/>
+    <col min="13" max="13" width="17.1640625" customWidth="1"/>
+    <col min="16" max="16" width="17.6640625" customWidth="1"/>
+    <col min="19" max="19" width="13.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:20" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:20" ht="22" x14ac:dyDescent="0.3">
+      <c r="B2" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="G2" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="I2" s="30"/>
+      <c r="J2" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="K2" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="30"/>
+      <c r="M2" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="O2" s="30"/>
+      <c r="P2" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q2" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="R2" s="30"/>
+      <c r="S2" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="T2" s="29" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B3" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" s="24">
+        <v>87.5</v>
+      </c>
+      <c r="D3" s="19" t="str">
+        <f>VLOOKUP(C3, grading_legend!$B$3:$E$7, 3, TRUE)</f>
+        <v>B</v>
+      </c>
+      <c r="E3" s="12">
+        <f>VLOOKUP(C3, grading_legend!$B$3:$E$7, 4, TRUE)</f>
+        <v>3</v>
+      </c>
+      <c r="G3" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="32">
+        <v>50</v>
+      </c>
+      <c r="I3" s="33"/>
+      <c r="J3" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="32">
+        <v>50</v>
+      </c>
+      <c r="L3" s="33"/>
+      <c r="M3" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="N3" s="34">
+        <v>100</v>
+      </c>
+      <c r="O3" s="33"/>
+      <c r="P3" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q3" s="34">
+        <v>100</v>
+      </c>
+      <c r="R3" s="33"/>
+      <c r="S3" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="T3" s="32">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B4" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="C4" s="24">
+        <v>87.5</v>
+      </c>
+      <c r="D4" s="19" t="str">
+        <f>VLOOKUP(C4, grading_legend!$B$3:$E$7, 3, TRUE)</f>
+        <v>B</v>
+      </c>
+      <c r="E4" s="12">
+        <f>VLOOKUP(C4, grading_legend!$B$3:$E$7, 4, TRUE)</f>
+        <v>3</v>
+      </c>
+      <c r="G4" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" s="32">
+        <v>50</v>
+      </c>
+      <c r="I4" s="33"/>
+      <c r="J4" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="K4" s="32">
+        <v>50</v>
+      </c>
+      <c r="L4" s="33"/>
+      <c r="M4" s="31" t="s">
+        <v>10</v>
+      </c>
+      <c r="N4" s="34">
+        <v>100</v>
+      </c>
+      <c r="O4" s="33"/>
+      <c r="P4" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q4" s="34">
+        <v>100</v>
+      </c>
+      <c r="R4" s="33"/>
+      <c r="S4" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="T4" s="35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="2:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="C5" s="19">
+        <v>100</v>
+      </c>
+      <c r="D5" s="19" t="str">
+        <f>VLOOKUP(C5, grading_legend!$B$3:$E$7, 3, TRUE)</f>
+        <v>A</v>
+      </c>
+      <c r="E5" s="12">
+        <f>VLOOKUP(C5, grading_legend!$B$3:$E$7, 4, TRUE)</f>
+        <v>4</v>
+      </c>
+      <c r="G5" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="32">
+        <v>50</v>
+      </c>
+      <c r="I5" s="33"/>
+      <c r="J5" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="K5" s="32">
+        <v>50</v>
+      </c>
+      <c r="L5" s="33"/>
+      <c r="M5" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="N5" s="34">
+        <v>100</v>
+      </c>
+      <c r="O5" s="33"/>
+      <c r="P5" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q5" s="37">
+        <v>100</v>
+      </c>
+      <c r="R5" s="33"/>
+      <c r="S5" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="T5" s="38">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B6" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="24">
+        <v>87.5</v>
+      </c>
+      <c r="D6" s="19" t="str">
+        <f>VLOOKUP(C6, grading_legend!$B$3:$E$7, 3, TRUE)</f>
+        <v>B</v>
+      </c>
+      <c r="E6" s="12">
+        <f>VLOOKUP(C6, grading_legend!$B$3:$E$7, 4, TRUE)</f>
+        <v>3</v>
+      </c>
+      <c r="G6" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" s="32">
+        <v>50</v>
+      </c>
+      <c r="I6" s="33"/>
+      <c r="J6" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="K6" s="32">
+        <v>50</v>
+      </c>
+      <c r="L6" s="33"/>
+      <c r="M6" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="N6" s="34">
+        <v>100</v>
+      </c>
+      <c r="O6" s="33"/>
+      <c r="P6" s="33"/>
+      <c r="Q6" s="33"/>
+      <c r="R6" s="33"/>
+      <c r="S6" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="T6" s="38">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="2:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" s="24">
+        <v>87.5</v>
+      </c>
+      <c r="D7" s="19" t="str">
+        <f>VLOOKUP(C7, grading_legend!$B$3:$E$7, 3, TRUE)</f>
+        <v>B</v>
+      </c>
+      <c r="E7" s="12">
+        <f>VLOOKUP(C7, grading_legend!$B$3:$E$7, 4, TRUE)</f>
+        <v>3</v>
+      </c>
+      <c r="G7" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="H7" s="32">
+        <v>50</v>
+      </c>
+      <c r="I7" s="33"/>
+      <c r="J7" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="K7" s="32">
+        <v>50</v>
+      </c>
+      <c r="L7" s="33"/>
+      <c r="M7" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="N7" s="37">
+        <v>100</v>
+      </c>
+      <c r="O7" s="33"/>
+      <c r="P7" s="33"/>
+      <c r="Q7" s="33"/>
+      <c r="R7" s="33"/>
+      <c r="S7" s="36" t="s">
+        <v>103</v>
+      </c>
+      <c r="T7" s="39">
+        <v>87.5</v>
+      </c>
+    </row>
+    <row r="8" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B8" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8" s="19">
+        <v>100</v>
+      </c>
+      <c r="D8" s="19" t="str">
+        <f>VLOOKUP(C8, grading_legend!$B$3:$E$7, 3, TRUE)</f>
+        <v>A</v>
+      </c>
+      <c r="E8" s="12">
+        <f>VLOOKUP(C8, grading_legend!$B$3:$E$7, 4, TRUE)</f>
+        <v>4</v>
+      </c>
+      <c r="G8" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8" s="32">
+        <v>50</v>
+      </c>
+      <c r="I8" s="33"/>
+      <c r="J8" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="K8" s="32">
+        <v>50</v>
+      </c>
+      <c r="L8" s="33"/>
+      <c r="M8" s="33"/>
+      <c r="N8" s="33"/>
+      <c r="O8" s="33"/>
+      <c r="P8" s="33"/>
+      <c r="Q8" s="33"/>
+      <c r="R8" s="33"/>
+      <c r="S8" s="33"/>
+      <c r="T8" s="33"/>
+    </row>
+    <row r="9" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B9" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" s="24">
+        <f>0.8*AVERAGE(C3,C4,C6,C7) + 0.2*AVERAGE(C5,C8)</f>
+        <v>90</v>
+      </c>
+      <c r="D9" s="19" t="str">
+        <f>VLOOKUP(C9, grading_legend!$B$3:$E$7, 3, TRUE)</f>
+        <v>A</v>
+      </c>
+      <c r="E9" s="12"/>
+      <c r="G9" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9" s="32">
+        <v>50</v>
+      </c>
+      <c r="I9" s="33"/>
+      <c r="J9" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="K9" s="32">
+        <v>50</v>
+      </c>
+      <c r="L9" s="33"/>
+      <c r="M9" s="33"/>
+      <c r="N9" s="33"/>
+      <c r="O9" s="33"/>
+      <c r="P9" s="33"/>
+      <c r="Q9" s="33"/>
+      <c r="R9" s="33"/>
+      <c r="S9" s="33"/>
+      <c r="T9" s="33"/>
+    </row>
+    <row r="10" spans="2:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10" s="19">
+        <f>VLOOKUP(C9, grading_legend!$B$3:$G$7, 6, TRUE)</f>
+        <v>3.5</v>
+      </c>
+      <c r="D10" s="19" t="str">
+        <f>VLOOKUP(C10, grading_legend!$G$3:$H$7, 2, TRUE)</f>
+        <v>A</v>
+      </c>
+      <c r="E10" s="12"/>
+      <c r="G10" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="H10" s="40">
+        <v>50</v>
+      </c>
+      <c r="I10" s="33"/>
+      <c r="J10" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="K10" s="40">
+        <v>50</v>
+      </c>
+      <c r="L10" s="33"/>
+      <c r="M10" s="33"/>
+      <c r="N10" s="33"/>
+      <c r="O10" s="33"/>
+      <c r="P10" s="33"/>
+      <c r="Q10" s="33"/>
+      <c r="R10" s="33"/>
+      <c r="S10" s="33"/>
+      <c r="T10" s="33"/>
+    </row>
+    <row r="11" spans="2:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C11" s="25" t="str">
+        <f>D10</f>
+        <v>A</v>
+      </c>
+      <c r="D11" s="25"/>
+      <c r="E11" s="14"/>
+    </row>
+    <row r="14" spans="2:20" ht="22" x14ac:dyDescent="0.3">
+      <c r="B14" s="41" t="s">
+        <v>109</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="C3:C9">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="lessThan">
+      <formula>75</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A36FBED0-DAD9-544A-8668-4C41B29B4227}">
   <dimension ref="B1:O10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -1440,13 +2108,13 @@
         <v>30</v>
       </c>
       <c r="C3" s="12">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="E3" s="11" t="s">
         <v>20</v>
       </c>
       <c r="F3" s="12">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H3" s="11" t="s">
         <v>9</v>
@@ -1465,7 +2133,7 @@
       </c>
       <c r="O3" s="12">
         <f>C10</f>
-        <v>74.142857142857139</v>
+        <v>63.714285714285715</v>
       </c>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.2">
@@ -1473,13 +2141,13 @@
         <v>31</v>
       </c>
       <c r="C4" s="12">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="E4" s="11" t="s">
         <v>21</v>
       </c>
       <c r="F4" s="12">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="H4" s="11" t="s">
         <v>10</v>
@@ -1498,7 +2166,7 @@
       </c>
       <c r="O4" s="15">
         <f>F10</f>
-        <v>74.142857142857139</v>
+        <v>67.142857142857139</v>
       </c>
     </row>
     <row r="5" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -1506,19 +2174,19 @@
         <v>32</v>
       </c>
       <c r="C5" s="12">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E5" s="11" t="s">
         <v>22</v>
       </c>
       <c r="F5" s="12">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="H5" s="11" t="s">
         <v>11</v>
       </c>
       <c r="I5" s="12">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="K5" s="13" t="s">
         <v>15</v>
@@ -1532,7 +2200,7 @@
       </c>
       <c r="O5" s="15">
         <f>I7</f>
-        <v>90.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.2">
@@ -1540,19 +2208,19 @@
         <v>33</v>
       </c>
       <c r="C6" s="12">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>23</v>
       </c>
       <c r="F6" s="12">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="H6" s="11" t="s">
         <v>27</v>
       </c>
       <c r="I6" s="12">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="N6" s="11" t="s">
         <v>19</v>
@@ -1567,27 +2235,27 @@
         <v>34</v>
       </c>
       <c r="C7" s="12">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E7" s="11" t="s">
         <v>24</v>
       </c>
       <c r="F7" s="12">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="H7" s="13" t="s">
         <v>12</v>
       </c>
       <c r="I7" s="14">
         <f>AVERAGE(I3:I6)</f>
-        <v>90.5</v>
+        <v>100</v>
       </c>
       <c r="N7" s="13" t="s">
         <v>103</v>
       </c>
       <c r="O7" s="16">
         <f>0.05*O3+0.2*O4+0.1*O5+0.65*O6</f>
-        <v>92.585714285714289</v>
+        <v>91.614285714285714</v>
       </c>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.2">
@@ -1595,13 +2263,13 @@
         <v>35</v>
       </c>
       <c r="C8" s="12">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E8" s="11" t="s">
         <v>25</v>
       </c>
       <c r="F8" s="12">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.2">
@@ -1609,13 +2277,13 @@
         <v>36</v>
       </c>
       <c r="C9" s="12">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F9" s="12">
-        <v>74</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -1624,17 +2292,547 @@
       </c>
       <c r="C10" s="14">
         <f>AVERAGE(C3:C9)</f>
-        <v>74.142857142857139</v>
+        <v>63.714285714285715</v>
       </c>
       <c r="E10" s="13" t="s">
         <v>8</v>
       </c>
       <c r="F10" s="14">
         <f>AVERAGE(F3:F9)</f>
-        <v>74.142857142857139</v>
+        <v>67.142857142857139</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="C3:C10">
+    <cfRule type="cellIs" dxfId="26" priority="2" operator="lessThan">
+      <formula>75</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:F10">
+    <cfRule type="cellIs" dxfId="9" priority="8" operator="lessThan">
+      <formula>75</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3:I7">
+    <cfRule type="cellIs" dxfId="8" priority="7" operator="lessThan">
+      <formula>75</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L3:L5">
+    <cfRule type="cellIs" dxfId="7" priority="6" operator="lessThan">
+      <formula>75</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O3:O7">
+    <cfRule type="cellIs" dxfId="25" priority="1" operator="lessThan">
+      <formula>75</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E17F2A36-E201-1A46-973C-1B0A9904F752}">
+  <dimension ref="B1:O8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="21.83203125" customWidth="1"/>
+    <col min="5" max="5" width="17.33203125" customWidth="1"/>
+    <col min="6" max="6" width="9.6640625" customWidth="1"/>
+    <col min="8" max="8" width="19.6640625" customWidth="1"/>
+    <col min="11" max="11" width="17.1640625" customWidth="1"/>
+    <col min="14" max="14" width="16.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:15" ht="19" x14ac:dyDescent="0.25">
+      <c r="B2" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="23"/>
+      <c r="E2" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="23"/>
+      <c r="H2" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="J2" s="23"/>
+      <c r="K2" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="L2" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="M2" s="23"/>
+      <c r="N2" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="O2" s="22" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B3" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="12">
+        <v>50</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" s="12">
+        <v>50</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="I3" s="12">
+        <v>100</v>
+      </c>
+      <c r="K3" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="L3" s="12">
+        <v>100</v>
+      </c>
+      <c r="N3" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="O3" s="12">
+        <f>C8</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B4" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="12">
+        <v>50</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="12">
+        <v>50</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="I4" s="12">
+        <v>100</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="L4" s="12">
+        <v>100</v>
+      </c>
+      <c r="N4" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="O4" s="15">
+        <f>F8</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="12">
+        <v>50</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" s="12">
+        <v>50</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="I5" s="12">
+        <v>100</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="L5" s="14">
+        <f>AVERAGE(L3:L4)</f>
+        <v>100</v>
+      </c>
+      <c r="N5" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="O5" s="15">
+        <f>I7</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B6" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="12">
+        <v>50</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" s="12">
+        <v>50</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="I6" s="12">
+        <v>100</v>
+      </c>
+      <c r="N6" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="O6" s="15">
+        <f>L5</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="12">
+        <v>50</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="12">
+        <v>50</v>
+      </c>
+      <c r="H7" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7" s="14">
+        <f>AVERAGE(I3:I6)</f>
+        <v>100</v>
+      </c>
+      <c r="N7" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="O7" s="16">
+        <f>0.05*O3+0.2*O4+0.1*O5+0.65*O6</f>
+        <v>87.5</v>
+      </c>
+    </row>
+    <row r="8" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="14">
+        <f>AVERAGE(C3:C7)</f>
+        <v>50</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="14">
+        <f>AVERAGE(F3:F7)</f>
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="C3:C8">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="lessThan">
+      <formula>75</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:F8">
+    <cfRule type="cellIs" dxfId="24" priority="8" operator="lessThan">
+      <formula>75</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3:I7">
+    <cfRule type="cellIs" dxfId="23" priority="7" operator="lessThan">
+      <formula>75</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L3:L5">
+    <cfRule type="cellIs" dxfId="22" priority="6" operator="lessThan">
+      <formula>75</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O3:O7">
+    <cfRule type="cellIs" dxfId="21" priority="1" operator="lessThan">
+      <formula>75</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E635A5A1-25A1-054E-80C4-0749F2070D13}">
+  <dimension ref="B1:O10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="21.83203125" customWidth="1"/>
+    <col min="5" max="5" width="17.33203125" customWidth="1"/>
+    <col min="8" max="8" width="16.33203125" customWidth="1"/>
+    <col min="11" max="11" width="17.33203125" customWidth="1"/>
+    <col min="14" max="14" width="17.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:15" ht="19" x14ac:dyDescent="0.25">
+      <c r="B2" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="23"/>
+      <c r="E2" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="23"/>
+      <c r="H2" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="J2" s="23"/>
+      <c r="K2" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="L2" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="M2" s="23"/>
+      <c r="N2" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="O2" s="22" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B3" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="12">
+        <v>50</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="F3" s="12">
+        <v>50</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="I3" s="12">
+        <v>100</v>
+      </c>
+      <c r="K3" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="L3" s="12">
+        <v>100</v>
+      </c>
+      <c r="N3" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="O3" s="12">
+        <f>C10</f>
+        <v>61.142857142857146</v>
+      </c>
+    </row>
+    <row r="4" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B4" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="12">
+        <v>50</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="12">
+        <v>60</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="I4" s="12">
+        <v>100</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="L4" s="12">
+        <v>100</v>
+      </c>
+      <c r="N4" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="O4" s="15">
+        <f>F10</f>
+        <v>63.142857142857146</v>
+      </c>
+    </row>
+    <row r="5" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="12">
+        <v>78</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F5" s="12">
+        <v>50</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="I5" s="12">
+        <v>100</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="L5" s="14">
+        <f>AVERAGE(L3:L4)</f>
+        <v>100</v>
+      </c>
+      <c r="N5" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="O5" s="15">
+        <f>I7</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B6" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="12">
+        <v>50</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F6" s="12">
+        <v>102</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="I6" s="12">
+        <v>100</v>
+      </c>
+      <c r="N6" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="O6" s="15">
+        <f>L5</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" s="12">
+        <v>50</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F7" s="12">
+        <v>50</v>
+      </c>
+      <c r="H7" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7" s="14">
+        <f>AVERAGE(I3:I6)</f>
+        <v>100</v>
+      </c>
+      <c r="N7" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="O7" s="16">
+        <f>0.05*O3+0.2*O4+0.1*O5+0.65*O6</f>
+        <v>90.685714285714283</v>
+      </c>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B8" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" s="12">
+        <v>100</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="F8" s="12">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B9" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" s="12">
+        <v>50</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="F9" s="12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="14">
+        <f>AVERAGE(C3:C9)</f>
+        <v>61.142857142857146</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="14">
+        <f>AVERAGE(F3:F9)</f>
+        <v>63.142857142857146</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="C3:C10">
     <cfRule type="cellIs" dxfId="20" priority="2" operator="lessThan">
       <formula>75</formula>
@@ -1664,17 +2862,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E17F2A36-E201-1A46-973C-1B0A9904F752}">
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CDF199B-E7AF-6043-A548-0DD6A3BF17EA}">
   <dimension ref="B1:O8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="21.83203125" customWidth="1"/>
-    <col min="5" max="5" width="17.33203125" customWidth="1"/>
-    <col min="6" max="6" width="9.6640625" customWidth="1"/>
-    <col min="8" max="8" width="19.6640625" customWidth="1"/>
+    <col min="2" max="2" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" customWidth="1"/>
+    <col min="8" max="8" width="16.83203125" customWidth="1"/>
     <col min="11" max="11" width="17.1640625" customWidth="1"/>
-    <col min="14" max="14" width="16.83203125" customWidth="1"/>
+    <col min="14" max="14" width="15.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -1716,157 +2913,157 @@
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B3" s="11" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="C3" s="12">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="F3" s="12">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="I3" s="12">
         <v>100</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="L3" s="12">
-        <v>64.5</v>
+        <v>100</v>
       </c>
       <c r="N3" s="11" t="s">
         <v>29</v>
       </c>
       <c r="O3" s="12">
         <f>C8</f>
-        <v>74</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B4" s="11" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="C4" s="12">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="F4" s="12">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="I4" s="12">
         <v>100</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="L4" s="12">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="N4" s="11" t="s">
         <v>6</v>
       </c>
       <c r="O4" s="15">
         <f>F8</f>
-        <v>73</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="11" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="C5" s="12">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E5" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="F5" s="12">
         <v>40</v>
       </c>
-      <c r="F5" s="12">
-        <v>100</v>
-      </c>
       <c r="H5" s="11" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="I5" s="12">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="K5" s="13" t="s">
         <v>15</v>
       </c>
       <c r="L5" s="14">
         <f>AVERAGE(L3:L4)</f>
-        <v>34.25</v>
+        <v>100</v>
       </c>
       <c r="N5" s="11" t="s">
         <v>13</v>
       </c>
       <c r="O5" s="15">
         <f>I7</f>
-        <v>90.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B6" s="11" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="C6" s="12">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>41</v>
+        <v>83</v>
       </c>
       <c r="F6" s="12">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="I6" s="12">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="N6" s="11" t="s">
         <v>19</v>
       </c>
       <c r="O6" s="15">
         <f>L5</f>
-        <v>34.25</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="C7" s="12">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="F7" s="12">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="H7" s="13" t="s">
         <v>12</v>
       </c>
       <c r="I7" s="14">
         <f>AVERAGE(I3:I6)</f>
-        <v>90.5</v>
+        <v>100</v>
       </c>
       <c r="N7" s="13" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="O7" s="16">
         <f>0.05*O3+0.2*O4+0.1*O5+0.65*O6</f>
-        <v>49.612499999999997</v>
+        <v>87.9</v>
       </c>
     </row>
     <row r="8" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -1875,17 +3072,18 @@
       </c>
       <c r="C8" s="14">
         <f>AVERAGE(C3:C7)</f>
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="E8" s="13" t="s">
         <v>8</v>
       </c>
       <c r="F8" s="14">
         <f>AVERAGE(F3:F7)</f>
-        <v>73</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="C3:C8">
     <cfRule type="cellIs" dxfId="15" priority="2" operator="lessThan">
       <formula>75</formula>
@@ -1915,536 +3113,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E635A5A1-25A1-054E-80C4-0749F2070D13}">
-  <dimension ref="B1:O10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="21.83203125" customWidth="1"/>
-    <col min="5" max="5" width="17.33203125" customWidth="1"/>
-    <col min="8" max="8" width="16.33203125" customWidth="1"/>
-    <col min="11" max="11" width="17.33203125" customWidth="1"/>
-    <col min="14" max="14" width="17.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:15" ht="19" x14ac:dyDescent="0.25">
-      <c r="B2" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="23"/>
-      <c r="E2" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="23"/>
-      <c r="H2" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="J2" s="23"/>
-      <c r="K2" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="L2" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="M2" s="23"/>
-      <c r="N2" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="O2" s="22" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B3" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" s="12">
-        <v>60</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="F3" s="12">
-        <v>60</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="I3" s="12">
-        <v>100</v>
-      </c>
-      <c r="K3" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="L3" s="12">
-        <v>100</v>
-      </c>
-      <c r="N3" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="O3" s="12">
-        <f>C10</f>
-        <v>74.142857142857139</v>
-      </c>
-    </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B4" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" s="12">
-        <v>70</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="F4" s="12">
-        <v>70</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="I4" s="12">
-        <v>100</v>
-      </c>
-      <c r="K4" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="L4" s="12">
-        <v>100</v>
-      </c>
-      <c r="N4" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="O4" s="15">
-        <f>F10</f>
-        <v>74.142857142857139</v>
-      </c>
-    </row>
-    <row r="5" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="C5" s="12">
-        <v>100</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="F5" s="12">
-        <v>100</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="I5" s="12">
-        <v>70</v>
-      </c>
-      <c r="K5" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="L5" s="14">
-        <f>AVERAGE(L3:L4)</f>
-        <v>100</v>
-      </c>
-      <c r="N5" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="O5" s="15">
-        <f>I7</f>
-        <v>90.5</v>
-      </c>
-    </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B6" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C6" s="12">
-        <v>95</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="F6" s="12">
-        <v>95</v>
-      </c>
-      <c r="H6" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="I6" s="12">
-        <v>92</v>
-      </c>
-      <c r="N6" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="O6" s="15">
-        <f>L5</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="C7" s="12">
-        <v>40</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="F7" s="12">
-        <v>40</v>
-      </c>
-      <c r="H7" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="I7" s="14">
-        <f>AVERAGE(I3:I6)</f>
-        <v>90.5</v>
-      </c>
-      <c r="N7" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="O7" s="16">
-        <f>0.05*O3+0.2*O4+0.1*O5+0.65*O6</f>
-        <v>92.585714285714289</v>
-      </c>
-    </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B8" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="C8" s="12">
-        <v>80</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="F8" s="12">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B9" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="C9" s="12">
-        <v>74</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="F9" s="12">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="10" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="14">
-        <f>AVERAGE(C3:C9)</f>
-        <v>74.142857142857139</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="14">
-        <f>AVERAGE(F3:F9)</f>
-        <v>74.142857142857139</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="C3:C10">
-    <cfRule type="cellIs" dxfId="10" priority="2" operator="lessThan">
-      <formula>75</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F3:F10">
-    <cfRule type="cellIs" dxfId="9" priority="8" operator="lessThan">
-      <formula>75</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I7">
-    <cfRule type="cellIs" dxfId="8" priority="7" operator="lessThan">
-      <formula>75</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L3:L5">
-    <cfRule type="cellIs" dxfId="7" priority="6" operator="lessThan">
-      <formula>75</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O3:O7">
-    <cfRule type="cellIs" dxfId="6" priority="1" operator="lessThan">
-      <formula>75</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CDF199B-E7AF-6043-A548-0DD6A3BF17EA}">
-  <dimension ref="B1:O8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" customWidth="1"/>
-    <col min="8" max="8" width="16.83203125" customWidth="1"/>
-    <col min="11" max="11" width="17.1640625" customWidth="1"/>
-    <col min="14" max="14" width="15.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:15" ht="19" x14ac:dyDescent="0.25">
-      <c r="B2" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="23"/>
-      <c r="E2" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="23"/>
-      <c r="H2" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="J2" s="23"/>
-      <c r="K2" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="L2" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="M2" s="23"/>
-      <c r="N2" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="O2" s="22" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B3" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C3" s="12">
-        <v>60</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="F3" s="12">
-        <v>60</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="I3" s="12">
-        <v>100</v>
-      </c>
-      <c r="K3" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="L3" s="12">
-        <v>100</v>
-      </c>
-      <c r="N3" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="O3" s="12">
-        <f>C8</f>
-        <v>73</v>
-      </c>
-    </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B4" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="C4" s="12">
-        <v>70</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="F4" s="12">
-        <v>70</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="I4" s="12">
-        <v>100</v>
-      </c>
-      <c r="K4" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="L4" s="12">
-        <v>100</v>
-      </c>
-      <c r="N4" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="O4" s="15">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="C5" s="12">
-        <v>100</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="F5" s="12">
-        <v>100</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="I5" s="12">
-        <v>70</v>
-      </c>
-      <c r="K5" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="L5" s="14">
-        <f>AVERAGE(L3:L4)</f>
-        <v>100</v>
-      </c>
-      <c r="N5" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="O5" s="15">
-        <f>I7</f>
-        <v>90.5</v>
-      </c>
-    </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B6" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" s="12">
-        <v>95</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="F6" s="12">
-        <v>95</v>
-      </c>
-      <c r="H6" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="I6" s="12">
-        <v>92</v>
-      </c>
-      <c r="N6" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="O6" s="15">
-        <f>L5</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="C7" s="12">
-        <v>40</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="F7" s="12">
-        <v>40</v>
-      </c>
-      <c r="H7" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="I7" s="14">
-        <f>AVERAGE(I3:I6)</f>
-        <v>90.5</v>
-      </c>
-      <c r="N7" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="O7" s="16">
-        <f>0.05*O3+0.2*O4+0.1*O5+0.65*O6</f>
-        <v>79.7</v>
-      </c>
-    </row>
-    <row r="8" spans="2:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="C8" s="14">
-        <f>AVERAGE(C3:C7)</f>
-        <v>73</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="14">
-        <f>AVERAGE(F3:F7)</f>
-        <v>73</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="C3:C8">
-    <cfRule type="cellIs" dxfId="5" priority="2" operator="lessThan">
-      <formula>75</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F3:F8">
-    <cfRule type="cellIs" dxfId="4" priority="8" operator="lessThan">
-      <formula>75</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I7">
-    <cfRule type="cellIs" dxfId="3" priority="7" operator="lessThan">
-      <formula>75</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L3:L5">
-    <cfRule type="cellIs" dxfId="2" priority="6" operator="lessThan">
-      <formula>75</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O3:O7">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <formula>75</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C63BB62-3B11-4042-9087-F9749BFF4B10}">
   <dimension ref="B1:H7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
